--- a/history_prices/MAR/prices_05032026.xlsx
+++ b/history_prices/MAR/prices_05032026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\GTA Petroleum\Еко България\Пламен - ексели\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23DFA266-3DD5-4229-A0F6-A22AF908BCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3DEBF5-6668-40C9-BB4F-1D87FA0D54F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЕКО БЮЛЕТИН" sheetId="1" r:id="rId1"/>
@@ -723,18 +723,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" customWidth="1"/>
+    <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" customWidth="1"/>
-    <col min="4" max="4" width="23.54296875" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" customWidth="1"/>
-    <col min="6" max="6" width="7.54296875" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -774,7 +774,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -791,7 +791,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -808,7 +808,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -825,7 +825,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -842,7 +842,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -859,7 +859,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -876,7 +876,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -893,7 +893,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -910,7 +910,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -927,7 +927,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -944,7 +944,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -961,7 +961,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -978,7 +978,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -995,7 +995,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>35</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>37</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>39</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>40</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>42</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>44</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>45</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>46</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>66</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>68</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>69</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>70</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>73</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>74</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>76</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>77</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>78</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>79</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>81</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>82</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>83</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>84</v>
       </c>
@@ -1634,7 +1634,7 @@
       <c r="F53" s="2"/>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>86</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="F54" s="2"/>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>88</v>
       </c>
@@ -1664,7 +1664,7 @@
       <c r="F55" s="2"/>
       <c r="G55" s="3"/>
     </row>
-    <row r="56" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>90</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="F56" s="2"/>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -1694,7 +1694,7 @@
       <c r="F57" s="2"/>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="F58" s="2"/>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>95</v>
       </c>
@@ -1724,7 +1724,7 @@
       <c r="F59" s="2"/>
       <c r="G59" s="3"/>
     </row>
-    <row r="60" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>99</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>101</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>102</v>
       </c>
@@ -1807,7 +1807,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="3"/>
     </row>
-    <row r="65" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>103</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="F65" s="2"/>
       <c r="G65" s="3"/>
     </row>
-    <row r="66" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>104</v>
       </c>

--- a/history_prices/MAR/prices_05032026.xlsx
+++ b/history_prices/MAR/prices_05032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3DEBF5-6668-40C9-BB4F-1D87FA0D54F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5359A5A7-BD06-43EE-BC42-B2204540D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/history_prices/MAR/prices_05032026.xlsx
+++ b/history_prices/MAR/prices_05032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5359A5A7-BD06-43EE-BC42-B2204540D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67DFA16-2619-4332-BDA1-652159AD6EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="135">
   <si>
     <t>ID</t>
   </si>
@@ -46,9 +46,6 @@
     <t>0001</t>
   </si>
   <si>
-    <t>Поди ЕООД</t>
-  </si>
-  <si>
     <t>Diesel EKONOMY</t>
   </si>
   <si>
@@ -61,78 +58,51 @@
     <t>0014</t>
   </si>
   <si>
-    <t>Док транс ЕООД</t>
-  </si>
-  <si>
     <t>0016</t>
   </si>
   <si>
     <t>0018</t>
   </si>
   <si>
-    <t>Веселин Стефанов Желязков ЗП</t>
-  </si>
-  <si>
     <t>0020</t>
   </si>
   <si>
     <t>0026</t>
   </si>
   <si>
-    <t>Мултиарт  ЕООД</t>
-  </si>
-  <si>
     <t>0028</t>
   </si>
   <si>
     <t>0034</t>
   </si>
   <si>
-    <t>Диляна –  02 ЕООД</t>
-  </si>
-  <si>
     <t>0038</t>
   </si>
   <si>
-    <t>Фуудс  трейд</t>
-  </si>
-  <si>
     <t>0040</t>
   </si>
   <si>
     <t>0046</t>
   </si>
   <si>
-    <t>Иво  Иванов ЧЗС</t>
-  </si>
-  <si>
     <t>0048</t>
   </si>
   <si>
     <t>0054</t>
   </si>
   <si>
-    <t>Поларис</t>
-  </si>
-  <si>
     <t>0056</t>
   </si>
   <si>
     <t>0058</t>
   </si>
   <si>
-    <t>Пантекс  агро ЕООД</t>
-  </si>
-  <si>
     <t>0060</t>
   </si>
   <si>
     <t>0083</t>
   </si>
   <si>
-    <t>Хранинвест</t>
-  </si>
-  <si>
     <t>0084</t>
   </si>
   <si>
@@ -151,9 +121,6 @@
     <t>0087</t>
   </si>
   <si>
-    <t>Спедстрой  ООД</t>
-  </si>
-  <si>
     <t>0088</t>
   </si>
   <si>
@@ -166,66 +133,42 @@
     <t>0095</t>
   </si>
   <si>
-    <t>Скала -  13 Стойчо Стойчев ЕТ</t>
-  </si>
-  <si>
     <t>0097</t>
   </si>
   <si>
     <t>0115</t>
   </si>
   <si>
-    <t>Ивон  Строй 2015 ЕООД</t>
-  </si>
-  <si>
     <t>0117</t>
   </si>
   <si>
     <t>0119</t>
   </si>
   <si>
-    <t>Анива</t>
-  </si>
-  <si>
     <t>0121</t>
   </si>
   <si>
     <t>0123</t>
   </si>
   <si>
-    <t>Автотранс  Петков</t>
-  </si>
-  <si>
     <t>0135</t>
   </si>
   <si>
-    <t>Меркурий  производство и Пакетаж АД</t>
-  </si>
-  <si>
     <t>0137</t>
   </si>
   <si>
     <t>0143</t>
   </si>
   <si>
-    <t>Евро  транс Премиум</t>
-  </si>
-  <si>
     <t>0147</t>
   </si>
   <si>
-    <t>БКС  Долни Чифлик</t>
-  </si>
-  <si>
     <t>0149</t>
   </si>
   <si>
     <t>0159</t>
   </si>
   <si>
-    <t>Демакс АД</t>
-  </si>
-  <si>
     <t>0160</t>
   </si>
   <si>
@@ -238,18 +181,12 @@
     <t>0167</t>
   </si>
   <si>
-    <t>Киров  тур еоод</t>
-  </si>
-  <si>
     <t>0169</t>
   </si>
   <si>
     <t>0171</t>
   </si>
   <si>
-    <t>Скимпрот</t>
-  </si>
-  <si>
     <t>0172</t>
   </si>
   <si>
@@ -262,9 +199,6 @@
     <t>0177</t>
   </si>
   <si>
-    <t>Демакс Ди Пи Ай АД</t>
-  </si>
-  <si>
     <t>0178</t>
   </si>
   <si>
@@ -277,33 +211,18 @@
     <t>0182</t>
   </si>
   <si>
-    <t>Фрозен  фуудс ЕООД</t>
-  </si>
-  <si>
     <t>0183</t>
   </si>
   <si>
-    <t>Комерс Нови Пазар ЕООД</t>
-  </si>
-  <si>
     <t>0184</t>
   </si>
   <si>
-    <t>Агропакт</t>
-  </si>
-  <si>
     <t>0186</t>
   </si>
   <si>
-    <t>Делор 20  ЕООД</t>
-  </si>
-  <si>
     <t>0188</t>
   </si>
   <si>
-    <t>Адига  ЕООД</t>
-  </si>
-  <si>
     <t>0189</t>
   </si>
   <si>
@@ -313,18 +232,12 @@
     <t>0191</t>
   </si>
   <si>
-    <t>Дианис ЕООД</t>
-  </si>
-  <si>
     <t>0193</t>
   </si>
   <si>
     <t>0194</t>
   </si>
   <si>
-    <t>Желязков инженеринг ЕООД</t>
-  </si>
-  <si>
     <t>0195</t>
   </si>
   <si>
@@ -335,6 +248,183 @@
   </si>
   <si>
     <t>0198</t>
+  </si>
+  <si>
+    <t>ЕИК</t>
+  </si>
+  <si>
+    <t>204195863</t>
+  </si>
+  <si>
+    <t>148078853</t>
+  </si>
+  <si>
+    <t>ПОДИ ЕООД</t>
+  </si>
+  <si>
+    <t>ДОК ТРАНС ЕООД</t>
+  </si>
+  <si>
+    <t>ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ</t>
+  </si>
+  <si>
+    <t>177947899</t>
+  </si>
+  <si>
+    <t>МУЛТИАРТ ЕООД</t>
+  </si>
+  <si>
+    <t>831339768</t>
+  </si>
+  <si>
+    <t>ДИЛЯНА-02 ЕООД</t>
+  </si>
+  <si>
+    <t>148100374</t>
+  </si>
+  <si>
+    <t>ФУУДС ТРЕЙД ЕООД</t>
+  </si>
+  <si>
+    <t>200448429</t>
+  </si>
+  <si>
+    <t>ИВО ИВАНОВ ЧЗС</t>
+  </si>
+  <si>
+    <t>124625506</t>
+  </si>
+  <si>
+    <t>ПОЛАРИС ЕООД</t>
+  </si>
+  <si>
+    <t>124699862</t>
+  </si>
+  <si>
+    <t>ПАНТЕКС АГРО ЕООД</t>
+  </si>
+  <si>
+    <t>202563608</t>
+  </si>
+  <si>
+    <t>ХРАНИНВЕСТ ЕООД</t>
+  </si>
+  <si>
+    <t>103582464</t>
+  </si>
+  <si>
+    <t>СПЕДСТРОЙ ООД</t>
+  </si>
+  <si>
+    <t>148117306</t>
+  </si>
+  <si>
+    <t>СКАЛА 13 - СТОЙЧО СТОЕВ ЕТ</t>
+  </si>
+  <si>
+    <t>030096387</t>
+  </si>
+  <si>
+    <t>ИВОН СТРОЙ 2015 ЕООД</t>
+  </si>
+  <si>
+    <t>206969652</t>
+  </si>
+  <si>
+    <t>АНИВА ЕООД</t>
+  </si>
+  <si>
+    <t>121282600</t>
+  </si>
+  <si>
+    <t>АВТОТРАНС ПЕТКОВ ЕООД</t>
+  </si>
+  <si>
+    <t>124644773</t>
+  </si>
+  <si>
+    <t>МЕРКУРИЙ ПРОИЗВОДСТВО И ПАКЕТАЖ АД</t>
+  </si>
+  <si>
+    <t>203968239</t>
+  </si>
+  <si>
+    <t>ЕВРО ТРАНС ПРЕМИУМ ЕООД</t>
+  </si>
+  <si>
+    <t>204195208</t>
+  </si>
+  <si>
+    <t>БКС ДОЛНИ ЧИФЛИК ЕООД</t>
+  </si>
+  <si>
+    <t>203347321</t>
+  </si>
+  <si>
+    <t>ДЕМАКС АД</t>
+  </si>
+  <si>
+    <t>831453003</t>
+  </si>
+  <si>
+    <t>КИРОВ ТУР ООД</t>
+  </si>
+  <si>
+    <t>207121152</t>
+  </si>
+  <si>
+    <t>СКИМПРОТ ООД</t>
+  </si>
+  <si>
+    <t>202727534</t>
+  </si>
+  <si>
+    <t>ДЕМАКС ДИ ПИ АЙ АД</t>
+  </si>
+  <si>
+    <t>175206054</t>
+  </si>
+  <si>
+    <t>ФРОЗЕН ФУУДС ЕООД</t>
+  </si>
+  <si>
+    <t>202217200</t>
+  </si>
+  <si>
+    <t>КОМЕРС НОВИ ПАЗАР ЕООД</t>
+  </si>
+  <si>
+    <t>127584370</t>
+  </si>
+  <si>
+    <t>АГРОПАКТ ЕООД</t>
+  </si>
+  <si>
+    <t>124698778</t>
+  </si>
+  <si>
+    <t>ДЕЛОР 20 ЕООД</t>
+  </si>
+  <si>
+    <t>207394655</t>
+  </si>
+  <si>
+    <t>АДИГА ЕООД</t>
+  </si>
+  <si>
+    <t>201684418</t>
+  </si>
+  <si>
+    <t>ДИЯНИС ВАРНА ООД</t>
+  </si>
+  <si>
+    <t>207384153</t>
+  </si>
+  <si>
+    <t>ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДСТВЕНИ СИСТЕМИ ЕООД</t>
+  </si>
+  <si>
+    <t>202151234</t>
   </si>
 </sst>
 </file>
@@ -405,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -420,6 +510,10 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,19 +816,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -744,1098 +839,1296 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="13">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="13">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="13">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="13">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="13">
+      <c r="G4" s="2"/>
+      <c r="H4" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="13">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="13">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="13">
+      <c r="G6" s="2"/>
+      <c r="H6" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="13">
+      <c r="G7" s="2"/>
+      <c r="H7" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="13">
+      <c r="G8" s="2"/>
+      <c r="H8" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="13">
+      <c r="G9" s="2"/>
+      <c r="H9" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="13">
+      <c r="G10" s="2"/>
+      <c r="H10" s="13">
         <v>1.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="13">
+      <c r="G11" s="2"/>
+      <c r="H11" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="13">
+      <c r="G12" s="2"/>
+      <c r="H12" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="13">
+      <c r="G13" s="2"/>
+      <c r="H13" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="13">
+      <c r="G14" s="2"/>
+      <c r="H14" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="13">
+      <c r="G15" s="2"/>
+      <c r="H15" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="13">
+      <c r="G16" s="2"/>
+      <c r="H16" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="13">
+      <c r="G17" s="2"/>
+      <c r="H17" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="13">
+      <c r="G18" s="2"/>
+      <c r="H18" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="9"/>
+        <v>95</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="F19" s="9"/>
-      <c r="G19" s="13">
+      <c r="G19" s="9"/>
+      <c r="H19" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="9"/>
+        <v>95</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="F20" s="9"/>
-      <c r="G20" s="13">
+      <c r="G20" s="9"/>
+      <c r="H20" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="13">
+        <v>95</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="13">
         <v>1.39</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="9"/>
+        <v>95</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="F22" s="9"/>
-      <c r="G22" s="13">
+      <c r="G22" s="9"/>
+      <c r="H22" s="13">
         <v>1.45</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="F23" s="6"/>
-      <c r="G23" s="13">
+      <c r="G23" s="6"/>
+      <c r="H23" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="F24" s="6"/>
-      <c r="G24" s="13">
+      <c r="G24" s="6"/>
+      <c r="H24" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="13">
+        <v>97</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="13">
         <v>1.39</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="F26" s="6"/>
-      <c r="G26" s="13">
+      <c r="G26" s="6"/>
+      <c r="H26" s="13">
         <v>1.45</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="13">
+      <c r="G27" s="2"/>
+      <c r="H27" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
       <c r="F28" s="2"/>
-      <c r="G28" s="13">
+      <c r="G28" s="2"/>
+      <c r="H28" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
       <c r="F29" s="2"/>
-      <c r="G29" s="13">
+      <c r="G29" s="2"/>
+      <c r="H29" s="13">
         <v>1.21</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
       <c r="F30" s="2"/>
-      <c r="G30" s="13">
+      <c r="G30" s="2"/>
+      <c r="H30" s="13">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
       <c r="F31" s="2"/>
-      <c r="G31" s="13">
+      <c r="G31" s="2"/>
+      <c r="H31" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="13">
+      <c r="G32" s="2"/>
+      <c r="H32" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
       <c r="F33" s="2"/>
-      <c r="G33" s="13">
+      <c r="G33" s="2"/>
+      <c r="H33" s="13">
         <v>1.2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
       <c r="F34" s="2"/>
-      <c r="G34" s="13">
+      <c r="G34" s="2"/>
+      <c r="H34" s="13">
         <v>1.21</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="13">
+      <c r="G35" s="2"/>
+      <c r="H35" s="13">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="13">
+      <c r="G36" s="2"/>
+      <c r="H36" s="13">
         <v>1.21</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
       <c r="F37" s="2"/>
-      <c r="G37" s="13">
+      <c r="G37" s="2"/>
+      <c r="H37" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
       <c r="F38" s="2"/>
-      <c r="G38" s="13">
+      <c r="G38" s="2"/>
+      <c r="H38" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="12"/>
+        <v>113</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="F39" s="12"/>
-      <c r="G39" s="13">
+      <c r="G39" s="12"/>
+      <c r="H39" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="12"/>
+        <v>113</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="F40" s="12"/>
-      <c r="G40" s="13">
+      <c r="G40" s="12"/>
+      <c r="H40" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="13">
+        <v>113</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="12"/>
+      <c r="H41" s="13">
         <v>1.39</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" s="10" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E42" s="12"/>
+        <v>113</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="F42" s="12"/>
-      <c r="G42" s="13">
+      <c r="G42" s="12"/>
+      <c r="H42" s="13">
         <v>1.45</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
       <c r="F43" s="2"/>
-      <c r="G43" s="13">
+      <c r="G43" s="2"/>
+      <c r="H43" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
       <c r="F44" s="2"/>
-      <c r="G44" s="13">
+      <c r="G44" s="2"/>
+      <c r="H44" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="9"/>
+        <v>117</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="F45" s="9"/>
-      <c r="G45" s="13">
+      <c r="G45" s="9"/>
+      <c r="H45" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="9"/>
+        <v>117</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="F46" s="9"/>
-      <c r="G46" s="13">
+      <c r="G46" s="9"/>
+      <c r="H46" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="13">
+        <v>117</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="9"/>
+      <c r="H47" s="13">
         <v>1.39</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="7" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E48" s="9"/>
+        <v>117</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="F48" s="9"/>
-      <c r="G48" s="13">
+      <c r="G48" s="9"/>
+      <c r="H48" s="13">
         <v>1.45</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="F49" s="6"/>
-      <c r="G49" s="13">
+      <c r="G49" s="6"/>
+      <c r="H49" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="F50" s="6"/>
-      <c r="G50" s="13">
+      <c r="G50" s="6"/>
+      <c r="H50" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="13">
+        <v>119</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="13">
         <v>1.39</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" s="4" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E52" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="F52" s="6"/>
-      <c r="G52" s="13">
+      <c r="G52" s="6"/>
+      <c r="H52" s="13">
         <v>1.45</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" t="s">
-        <v>85</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
       <c r="F53" s="2"/>
-      <c r="G53" s="3"/>
-    </row>
-    <row r="54" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="2"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" t="s">
-        <v>87</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="2"/>
-      <c r="G54" s="3"/>
-    </row>
-    <row r="55" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="2"/>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
       <c r="F55" s="2"/>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55" s="2"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
       <c r="F56" s="2"/>
-      <c r="G56" s="3"/>
-    </row>
-    <row r="57" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56" s="2"/>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" t="s">
-        <v>93</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
       <c r="F57" s="2"/>
-      <c r="G57" s="3"/>
-    </row>
-    <row r="58" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57" s="2"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
       <c r="F58" s="2"/>
-      <c r="G58" s="3"/>
-    </row>
-    <row r="59" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G58" s="2"/>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
       <c r="F59" s="2"/>
-      <c r="G59" s="3"/>
-    </row>
-    <row r="60" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="2"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" t="s">
-        <v>97</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
       <c r="F60" s="2"/>
-      <c r="G60" s="13">
+      <c r="G60" s="2"/>
+      <c r="H60" s="13">
         <v>1.22</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" t="s">
-        <v>97</v>
-      </c>
-      <c r="D61" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
       <c r="F61" s="2"/>
-      <c r="G61" s="13">
+      <c r="G61" s="2"/>
+      <c r="H61" s="13">
         <v>1.17</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" t="s">
-        <v>100</v>
-      </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
       <c r="F62" s="2"/>
-      <c r="G62" s="13">
+      <c r="G62" s="2"/>
+      <c r="H62" s="13">
         <v>1.23</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D63" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
       <c r="F63" s="2"/>
-      <c r="G63" s="13">
+      <c r="G63" s="2"/>
+      <c r="H63" s="13">
         <v>1.18</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" t="s">
-        <v>93</v>
-      </c>
-      <c r="D64" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
       <c r="F64" s="2"/>
-      <c r="G64" s="3"/>
-    </row>
-    <row r="65" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G64" s="2"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
       <c r="F65" s="2"/>
-      <c r="G65" s="3"/>
-    </row>
-    <row r="66" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G65" s="2"/>
+      <c r="H65" s="3"/>
+    </row>
+    <row r="66" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" t="s">
-        <v>87</v>
-      </c>
-      <c r="D66" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
       <c r="F66" s="2"/>
-      <c r="G66" s="3"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
